--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -889,37 +889,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126932059</v>
+        <v>126930782</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>57479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>102976</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -928,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586799</v>
+        <v>586748</v>
       </c>
       <c r="R4" t="n">
-        <v>6931194</v>
+        <v>6931372</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flyger över oss och gör läten</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,38 +996,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126930782</v>
+        <v>126932059</v>
       </c>
       <c r="B5" t="n">
-        <v>57479</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102976</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1030,13 +1035,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586748</v>
+        <v>586799</v>
       </c>
       <c r="R5" t="n">
-        <v>6931372</v>
+        <v>6931194</v>
       </c>
       <c r="S5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,11 +1071,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flyger över oss och gör läten</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1418,27 +1418,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126929962</v>
+        <v>126932136</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57479</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>102976</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1446,10 +1446,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1458,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586797</v>
+        <v>586790</v>
       </c>
       <c r="R9" t="n">
-        <v>6931496</v>
+        <v>6931174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,7 +1502,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Flyger ovanför oss.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,27 +1529,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126932136</v>
+        <v>126929962</v>
       </c>
       <c r="B10" t="n">
-        <v>57479</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1553,14 +1557,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586790</v>
+        <v>586797</v>
       </c>
       <c r="R10" t="n">
-        <v>6931174</v>
+        <v>6931496</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flyger ovanför oss.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1636,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126930561</v>
+        <v>126930308</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586743</v>
+        <v>586754</v>
       </c>
       <c r="R11" t="n">
-        <v>6931411</v>
+        <v>6931449</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,10 +1733,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126930308</v>
+        <v>126930561</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586754</v>
+        <v>586743</v>
       </c>
       <c r="R12" t="n">
-        <v>6931449</v>
+        <v>6931411</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,7 +1833,7 @@
         <v>126929931</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,37 +1927,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126930960</v>
+        <v>126930379</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1966,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586776</v>
+        <v>586799</v>
       </c>
       <c r="R14" t="n">
-        <v>6931363</v>
+        <v>6931409</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,6 +2003,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2028,7 +2034,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126930379</v>
+        <v>126930081</v>
       </c>
       <c r="B15" t="n">
         <v>57657</v>
@@ -2068,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586799</v>
+        <v>586766</v>
       </c>
       <c r="R15" t="n">
-        <v>6931409</v>
+        <v>6931484</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,38 +2141,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126930081</v>
+        <v>126930960</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>98436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2175,10 +2180,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586766</v>
+        <v>586776</v>
       </c>
       <c r="R16" t="n">
-        <v>6931484</v>
+        <v>6931363</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2211,11 +2216,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2349,10 +2349,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126930790</v>
+        <v>126932045</v>
       </c>
       <c r="B18" t="n">
-        <v>57817</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2360,42 +2360,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586748</v>
+        <v>586799</v>
       </c>
       <c r="R18" t="n">
-        <v>6931372</v>
+        <v>6931194</v>
       </c>
       <c r="S18" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2451,10 +2446,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126932045</v>
+        <v>126930790</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>57817</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2462,37 +2457,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586799</v>
+        <v>586748</v>
       </c>
       <c r="R19" t="n">
-        <v>6931194</v>
+        <v>6931372</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2762,10 +2762,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126932116</v>
+        <v>126931781</v>
       </c>
       <c r="B22" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>110</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586789</v>
+        <v>586763</v>
       </c>
       <c r="R22" t="n">
-        <v>6931181</v>
+        <v>6931228</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,6 +2837,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Blommar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2863,45 +2868,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126931990</v>
+        <v>126932116</v>
       </c>
       <c r="B23" t="n">
-        <v>78739</v>
+        <v>98436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586783</v>
+        <v>586789</v>
       </c>
       <c r="R23" t="n">
-        <v>6931194</v>
+        <v>6931181</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2960,37 +2969,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126931781</v>
+        <v>126931480</v>
       </c>
       <c r="B24" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>110</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2999,10 +3009,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586763</v>
+        <v>586733</v>
       </c>
       <c r="R24" t="n">
-        <v>6931228</v>
+        <v>6931251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3039,7 +3049,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Blommar</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3066,7 +3076,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126931480</v>
+        <v>126932091</v>
       </c>
       <c r="B25" t="n">
         <v>57657</v>
@@ -3097,7 +3107,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3106,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586733</v>
+        <v>586794</v>
       </c>
       <c r="R25" t="n">
-        <v>6931251</v>
+        <v>6931188</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3146,7 +3156,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3173,10 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126932091</v>
+        <v>126931990</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>78770</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3184,39 +3194,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586794</v>
+        <v>586783</v>
       </c>
       <c r="R26" t="n">
-        <v>6931188</v>
+        <v>6931194</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3249,11 +3254,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3283,7 +3283,7 @@
         <v>126931803</v>
       </c>
       <c r="B27" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,45 +3387,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126929983</v>
+        <v>126930037</v>
       </c>
       <c r="B28" t="n">
-        <v>98281</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586788</v>
+        <v>586781</v>
       </c>
       <c r="R28" t="n">
-        <v>6931484</v>
+        <v>6931476</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,45 +3484,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126930037</v>
+        <v>126929983</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>98356</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586781</v>
+        <v>586788</v>
       </c>
       <c r="R29" t="n">
-        <v>6931476</v>
+        <v>6931484</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3584,7 +3584,7 @@
         <v>126930443</v>
       </c>
       <c r="B30" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>126932059</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>126930308</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>126930561</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>126929931</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>126930960</v>
       </c>
       <c r="B16" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126932045</v>
+        <v>126930790</v>
       </c>
       <c r="B18" t="n">
-        <v>79011</v>
+        <v>57817</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2360,37 +2360,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586799</v>
+        <v>586748</v>
       </c>
       <c r="R18" t="n">
-        <v>6931194</v>
+        <v>6931372</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2446,10 +2451,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126930790</v>
+        <v>126932045</v>
       </c>
       <c r="B19" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2457,42 +2462,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586748</v>
+        <v>586799</v>
       </c>
       <c r="R19" t="n">
-        <v>6931372</v>
+        <v>6931194</v>
       </c>
       <c r="S19" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2762,10 +2762,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126931781</v>
+        <v>126932116</v>
       </c>
       <c r="B22" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586763</v>
+        <v>586789</v>
       </c>
       <c r="R22" t="n">
-        <v>6931228</v>
+        <v>6931181</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,11 +2837,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Blommar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2868,37 +2863,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126932116</v>
+        <v>126931480</v>
       </c>
       <c r="B23" t="n">
-        <v>98436</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2907,10 +2903,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586789</v>
+        <v>586733</v>
       </c>
       <c r="R23" t="n">
-        <v>6931181</v>
+        <v>6931251</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,6 +2939,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2969,7 +2970,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126931480</v>
+        <v>126932091</v>
       </c>
       <c r="B24" t="n">
         <v>57657</v>
@@ -3000,7 +3001,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3009,10 +3010,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586733</v>
+        <v>586794</v>
       </c>
       <c r="R24" t="n">
-        <v>6931251</v>
+        <v>6931188</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3049,7 +3050,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3076,38 +3077,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126932091</v>
+        <v>126931781</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>98442</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>110</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586794</v>
+        <v>586763</v>
       </c>
       <c r="R25" t="n">
-        <v>6931188</v>
+        <v>6931228</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Blommar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3186,7 +3186,7 @@
         <v>126931990</v>
       </c>
       <c r="B26" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>126931803</v>
       </c>
       <c r="B27" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,45 +3387,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126930037</v>
+        <v>126929983</v>
       </c>
       <c r="B28" t="n">
-        <v>79011</v>
+        <v>98362</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586781</v>
+        <v>586788</v>
       </c>
       <c r="R28" t="n">
-        <v>6931476</v>
+        <v>6931484</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,45 +3484,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126929983</v>
+        <v>126930037</v>
       </c>
       <c r="B29" t="n">
-        <v>98356</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586788</v>
+        <v>586781</v>
       </c>
       <c r="R29" t="n">
-        <v>6931484</v>
+        <v>6931476</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3584,7 +3584,7 @@
         <v>126930443</v>
       </c>
       <c r="B30" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -889,38 +889,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126930782</v>
+        <v>126932059</v>
       </c>
       <c r="B4" t="n">
-        <v>57479</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102976</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -929,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586748</v>
+        <v>586799</v>
       </c>
       <c r="R4" t="n">
-        <v>6931372</v>
+        <v>6931194</v>
       </c>
       <c r="S4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,11 +964,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flyger över oss och gör läten</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,37 +990,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126932059</v>
+        <v>126930782</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>57479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102976</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1035,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586799</v>
+        <v>586748</v>
       </c>
       <c r="R5" t="n">
-        <v>6931194</v>
+        <v>6931372</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,6 +1066,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flyger över oss och gör läten</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1418,27 +1418,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126932136</v>
+        <v>126929962</v>
       </c>
       <c r="B9" t="n">
-        <v>57479</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1446,14 +1446,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1462,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586790</v>
+        <v>586797</v>
       </c>
       <c r="R9" t="n">
-        <v>6931174</v>
+        <v>6931496</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1498,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Flyger ovanför oss.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,27 +1525,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126929962</v>
+        <v>126932136</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57479</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>102976</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1557,10 +1553,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586797</v>
+        <v>586790</v>
       </c>
       <c r="R10" t="n">
-        <v>6931496</v>
+        <v>6931174</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Flyger ovanför oss.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2349,10 +2349,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126930790</v>
+        <v>126932045</v>
       </c>
       <c r="B18" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2360,42 +2360,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586748</v>
+        <v>586799</v>
       </c>
       <c r="R18" t="n">
-        <v>6931372</v>
+        <v>6931194</v>
       </c>
       <c r="S18" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2451,10 +2446,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126932045</v>
+        <v>126930790</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2462,37 +2457,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586799</v>
+        <v>586748</v>
       </c>
       <c r="R19" t="n">
-        <v>6931194</v>
+        <v>6931372</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2762,37 +2762,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126932116</v>
+        <v>126931480</v>
       </c>
       <c r="B22" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2801,10 +2802,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586789</v>
+        <v>586733</v>
       </c>
       <c r="R22" t="n">
-        <v>6931181</v>
+        <v>6931251</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,6 +2838,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2863,7 +2869,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126931480</v>
+        <v>126932091</v>
       </c>
       <c r="B23" t="n">
         <v>57657</v>
@@ -2894,7 +2900,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2903,10 +2909,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586733</v>
+        <v>586794</v>
       </c>
       <c r="R23" t="n">
-        <v>6931251</v>
+        <v>6931188</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,7 +2949,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2970,38 +2976,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126932091</v>
+        <v>126931781</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>98442</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>110</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3010,10 +3015,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586794</v>
+        <v>586763</v>
       </c>
       <c r="R24" t="n">
-        <v>6931188</v>
+        <v>6931228</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3050,7 +3055,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Blommar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3077,49 +3082,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126931781</v>
+        <v>126931990</v>
       </c>
       <c r="B25" t="n">
-        <v>98442</v>
+        <v>78773</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586763</v>
+        <v>586783</v>
       </c>
       <c r="R25" t="n">
-        <v>6931228</v>
+        <v>6931194</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,11 +3153,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Blommar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,45 +3179,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126931990</v>
+        <v>126932116</v>
       </c>
       <c r="B26" t="n">
-        <v>78773</v>
+        <v>98442</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586783</v>
+        <v>586789</v>
       </c>
       <c r="R26" t="n">
-        <v>6931194</v>
+        <v>6931181</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -2762,10 +2762,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126931480</v>
+        <v>126931990</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>78773</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2773,39 +2773,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586733</v>
+        <v>586783</v>
       </c>
       <c r="R22" t="n">
-        <v>6931251</v>
+        <v>6931194</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2838,11 +2833,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2869,38 +2859,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126932091</v>
+        <v>126932116</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>98442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2909,10 +2898,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586794</v>
+        <v>586789</v>
       </c>
       <c r="R23" t="n">
-        <v>6931188</v>
+        <v>6931181</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2945,11 +2934,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2976,37 +2960,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126931781</v>
+        <v>126931480</v>
       </c>
       <c r="B24" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>110</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3015,10 +3000,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586763</v>
+        <v>586733</v>
       </c>
       <c r="R24" t="n">
-        <v>6931228</v>
+        <v>6931251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3055,7 +3040,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Blommar</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3082,10 +3067,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126931990</v>
+        <v>126932091</v>
       </c>
       <c r="B25" t="n">
-        <v>78773</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3093,34 +3078,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586783</v>
+        <v>586794</v>
       </c>
       <c r="R25" t="n">
-        <v>6931194</v>
+        <v>6931188</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3153,6 +3143,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3179,7 +3174,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126932116</v>
+        <v>126931781</v>
       </c>
       <c r="B26" t="n">
         <v>98442</v>
@@ -3209,7 +3204,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>110</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3218,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586789</v>
+        <v>586763</v>
       </c>
       <c r="R26" t="n">
-        <v>6931181</v>
+        <v>6931228</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3254,6 +3249,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Blommar</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>126932059</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>126930960</v>
       </c>
       <c r="B16" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2762,10 +2762,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126931990</v>
+        <v>126932091</v>
       </c>
       <c r="B22" t="n">
-        <v>78773</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2773,34 +2773,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586783</v>
+        <v>586794</v>
       </c>
       <c r="R22" t="n">
-        <v>6931194</v>
+        <v>6931188</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2833,6 +2838,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2859,37 +2869,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126932116</v>
+        <v>126931480</v>
       </c>
       <c r="B23" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2898,10 +2909,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586789</v>
+        <v>586733</v>
       </c>
       <c r="R23" t="n">
-        <v>6931181</v>
+        <v>6931251</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,6 +2945,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2960,38 +2976,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126931480</v>
+        <v>126931781</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>110</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3000,10 +3015,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586733</v>
+        <v>586763</v>
       </c>
       <c r="R24" t="n">
-        <v>6931251</v>
+        <v>6931228</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3040,7 +3055,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Blommar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3067,38 +3082,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126932091</v>
+        <v>126932116</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3107,10 +3121,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586794</v>
+        <v>586789</v>
       </c>
       <c r="R25" t="n">
-        <v>6931188</v>
+        <v>6931181</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,11 +3157,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3174,49 +3183,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126931781</v>
+        <v>126931990</v>
       </c>
       <c r="B26" t="n">
-        <v>98442</v>
+        <v>78773</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586763</v>
+        <v>586783</v>
       </c>
       <c r="R26" t="n">
-        <v>6931228</v>
+        <v>6931194</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3249,11 +3254,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Blommar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3283,7 +3283,7 @@
         <v>126931803</v>
       </c>
       <c r="B27" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,45 +3387,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126929983</v>
+        <v>126930037</v>
       </c>
       <c r="B28" t="n">
-        <v>98362</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586788</v>
+        <v>586781</v>
       </c>
       <c r="R28" t="n">
-        <v>6931484</v>
+        <v>6931476</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,45 +3484,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126930037</v>
+        <v>126929983</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>98363</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586781</v>
+        <v>586788</v>
       </c>
       <c r="R29" t="n">
-        <v>6931476</v>
+        <v>6931484</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3584,7 +3584,7 @@
         <v>126930443</v>
       </c>
       <c r="B30" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -1418,27 +1418,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126929962</v>
+        <v>126932136</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57479</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>102976</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1446,10 +1446,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1458,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586797</v>
+        <v>586790</v>
       </c>
       <c r="R9" t="n">
-        <v>6931496</v>
+        <v>6931174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,7 +1502,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Flyger ovanför oss.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,27 +1529,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126932136</v>
+        <v>126929962</v>
       </c>
       <c r="B10" t="n">
-        <v>57479</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1553,14 +1557,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586790</v>
+        <v>586797</v>
       </c>
       <c r="R10" t="n">
-        <v>6931174</v>
+        <v>6931496</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flyger ovanför oss.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2762,38 +2762,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126932091</v>
+        <v>126931781</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>110</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2802,10 +2801,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586794</v>
+        <v>586763</v>
       </c>
       <c r="R22" t="n">
-        <v>6931188</v>
+        <v>6931228</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,7 +2841,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Blommar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2869,38 +2868,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126931480</v>
+        <v>126932116</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2909,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586733</v>
+        <v>586789</v>
       </c>
       <c r="R23" t="n">
-        <v>6931251</v>
+        <v>6931181</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2945,11 +2943,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2976,49 +2969,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126931781</v>
+        <v>126931990</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586763</v>
+        <v>586783</v>
       </c>
       <c r="R24" t="n">
-        <v>6931228</v>
+        <v>6931194</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3051,11 +3040,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Blommar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3082,37 +3066,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126932116</v>
+        <v>126931480</v>
       </c>
       <c r="B25" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3121,10 +3106,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586789</v>
+        <v>586733</v>
       </c>
       <c r="R25" t="n">
-        <v>6931181</v>
+        <v>6931251</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3157,6 +3142,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,10 +3173,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126931990</v>
+        <v>126932091</v>
       </c>
       <c r="B26" t="n">
-        <v>78773</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3194,34 +3184,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586783</v>
+        <v>586794</v>
       </c>
       <c r="R26" t="n">
-        <v>6931194</v>
+        <v>6931188</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3254,6 +3249,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -889,37 +889,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126932059</v>
+        <v>126930782</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>57479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>102976</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -928,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586799</v>
+        <v>586748</v>
       </c>
       <c r="R4" t="n">
-        <v>6931194</v>
+        <v>6931372</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flyger över oss och gör läten</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,38 +996,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126930782</v>
+        <v>126932059</v>
       </c>
       <c r="B5" t="n">
-        <v>57479</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102976</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1030,13 +1035,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586748</v>
+        <v>586799</v>
       </c>
       <c r="R5" t="n">
-        <v>6931372</v>
+        <v>6931194</v>
       </c>
       <c r="S5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,11 +1071,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flyger över oss och gör läten</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1418,27 +1418,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126932136</v>
+        <v>126929962</v>
       </c>
       <c r="B9" t="n">
-        <v>57479</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1446,14 +1446,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1462,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586790</v>
+        <v>586797</v>
       </c>
       <c r="R9" t="n">
-        <v>6931174</v>
+        <v>6931496</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1498,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Flyger ovanför oss.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,27 +1525,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126929962</v>
+        <v>126932136</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57479</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>102976</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1557,10 +1553,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586797</v>
+        <v>586790</v>
       </c>
       <c r="R10" t="n">
-        <v>6931496</v>
+        <v>6931174</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Flyger ovanför oss.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2349,10 +2349,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126932045</v>
+        <v>126930790</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2360,37 +2360,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586799</v>
+        <v>586748</v>
       </c>
       <c r="R18" t="n">
-        <v>6931194</v>
+        <v>6931372</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2446,10 +2451,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126930790</v>
+        <v>126932045</v>
       </c>
       <c r="B19" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2457,42 +2462,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586748</v>
+        <v>586799</v>
       </c>
       <c r="R19" t="n">
-        <v>6931372</v>
+        <v>6931194</v>
       </c>
       <c r="S19" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2762,37 +2762,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126931781</v>
+        <v>126931480</v>
       </c>
       <c r="B22" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>110</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2801,10 +2802,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586763</v>
+        <v>586733</v>
       </c>
       <c r="R22" t="n">
-        <v>6931228</v>
+        <v>6931251</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2841,7 +2842,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Blommar</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2868,37 +2869,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126932116</v>
+        <v>126932091</v>
       </c>
       <c r="B23" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2907,10 +2909,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586789</v>
+        <v>586794</v>
       </c>
       <c r="R23" t="n">
-        <v>6931181</v>
+        <v>6931188</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,6 +2945,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2969,45 +2976,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126931990</v>
+        <v>126931781</v>
       </c>
       <c r="B24" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586783</v>
+        <v>586763</v>
       </c>
       <c r="R24" t="n">
-        <v>6931194</v>
+        <v>6931228</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3040,6 +3051,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Blommar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3066,38 +3082,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126931480</v>
+        <v>126932116</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3106,10 +3121,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586733</v>
+        <v>586789</v>
       </c>
       <c r="R25" t="n">
-        <v>6931251</v>
+        <v>6931181</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3142,11 +3157,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3173,10 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126932091</v>
+        <v>126931990</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>78773</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3184,39 +3194,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586794</v>
+        <v>586783</v>
       </c>
       <c r="R26" t="n">
-        <v>6931188</v>
+        <v>6931194</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3249,11 +3254,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3387,45 +3387,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126930037</v>
+        <v>126929983</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>98363</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586781</v>
+        <v>586788</v>
       </c>
       <c r="R28" t="n">
-        <v>6931476</v>
+        <v>6931484</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,45 +3484,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126929983</v>
+        <v>126930037</v>
       </c>
       <c r="B29" t="n">
-        <v>98363</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586788</v>
+        <v>586781</v>
       </c>
       <c r="R29" t="n">
-        <v>6931484</v>
+        <v>6931476</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -1418,27 +1418,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126929962</v>
+        <v>126932136</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57479</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>102976</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1446,10 +1446,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1458,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586797</v>
+        <v>586790</v>
       </c>
       <c r="R9" t="n">
-        <v>6931496</v>
+        <v>6931174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,7 +1502,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Flyger ovanför oss.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,27 +1529,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126932136</v>
+        <v>126929962</v>
       </c>
       <c r="B10" t="n">
-        <v>57479</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1553,14 +1557,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586790</v>
+        <v>586797</v>
       </c>
       <c r="R10" t="n">
-        <v>6931174</v>
+        <v>6931496</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flyger ovanför oss.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1927,38 +1927,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126930379</v>
+        <v>126930960</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1967,10 +1966,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586799</v>
+        <v>586776</v>
       </c>
       <c r="R14" t="n">
-        <v>6931409</v>
+        <v>6931363</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2003,11 +2002,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2034,7 +2028,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126930081</v>
+        <v>126930379</v>
       </c>
       <c r="B15" t="n">
         <v>57657</v>
@@ -2074,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586766</v>
+        <v>586799</v>
       </c>
       <c r="R15" t="n">
-        <v>6931484</v>
+        <v>6931409</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,37 +2135,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126930960</v>
+        <v>126930081</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2180,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586776</v>
+        <v>586766</v>
       </c>
       <c r="R16" t="n">
-        <v>6931363</v>
+        <v>6931484</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2216,6 +2211,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2976,49 +2976,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126931781</v>
+        <v>126931990</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586763</v>
+        <v>586783</v>
       </c>
       <c r="R24" t="n">
-        <v>6931228</v>
+        <v>6931194</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3051,11 +3047,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Blommar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3082,7 +3073,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126932116</v>
+        <v>126931781</v>
       </c>
       <c r="B25" t="n">
         <v>98443</v>
@@ -3112,7 +3103,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>110</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3121,10 +3112,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586789</v>
+        <v>586763</v>
       </c>
       <c r="R25" t="n">
-        <v>6931181</v>
+        <v>6931228</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3157,6 +3148,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Blommar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,45 +3179,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126931990</v>
+        <v>126932116</v>
       </c>
       <c r="B26" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586783</v>
+        <v>586789</v>
       </c>
       <c r="R26" t="n">
-        <v>6931194</v>
+        <v>6931181</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -1927,37 +1927,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126930960</v>
+        <v>126930379</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1966,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586776</v>
+        <v>586799</v>
       </c>
       <c r="R14" t="n">
-        <v>6931363</v>
+        <v>6931409</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,6 +2003,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2028,7 +2034,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126930379</v>
+        <v>126930081</v>
       </c>
       <c r="B15" t="n">
         <v>57657</v>
@@ -2068,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586799</v>
+        <v>586766</v>
       </c>
       <c r="R15" t="n">
-        <v>6931409</v>
+        <v>6931484</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,38 +2141,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126930081</v>
+        <v>126930960</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2175,10 +2180,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586766</v>
+        <v>586776</v>
       </c>
       <c r="R16" t="n">
-        <v>6931484</v>
+        <v>6931363</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2211,11 +2216,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3387,45 +3387,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126929983</v>
+        <v>126930037</v>
       </c>
       <c r="B28" t="n">
-        <v>98363</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586788</v>
+        <v>586781</v>
       </c>
       <c r="R28" t="n">
-        <v>6931484</v>
+        <v>6931476</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,45 +3484,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126930037</v>
+        <v>126929983</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>98363</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586781</v>
+        <v>586788</v>
       </c>
       <c r="R29" t="n">
-        <v>6931476</v>
+        <v>6931484</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126930713</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126932017</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126930782</v>
       </c>
       <c r="B4" t="n">
-        <v>57479</v>
+        <v>57483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126932059</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>126931093</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>126930683</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>126931252</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,27 +1418,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126932136</v>
+        <v>126929962</v>
       </c>
       <c r="B9" t="n">
-        <v>57479</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1446,14 +1446,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1462,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586790</v>
+        <v>586797</v>
       </c>
       <c r="R9" t="n">
-        <v>6931174</v>
+        <v>6931496</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1498,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Flyger ovanför oss.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,27 +1525,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126929962</v>
+        <v>126932136</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>102976</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1557,10 +1553,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586797</v>
+        <v>586790</v>
       </c>
       <c r="R10" t="n">
-        <v>6931496</v>
+        <v>6931174</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Flyger ovanför oss.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,7 +1639,7 @@
         <v>126930308</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>126930561</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>126929931</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>126930379</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>126930081</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>126930960</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>126931404</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>126930790</v>
       </c>
       <c r="B18" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>126932045</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>126930476</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>126931316</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2762,10 +2762,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126931480</v>
+        <v>126931990</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>78777</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2773,39 +2773,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586733</v>
+        <v>586783</v>
       </c>
       <c r="R22" t="n">
-        <v>6931251</v>
+        <v>6931194</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2838,11 +2833,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2869,10 +2859,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126932091</v>
+        <v>126931480</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,7 +2890,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2909,10 +2899,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586794</v>
+        <v>586733</v>
       </c>
       <c r="R23" t="n">
-        <v>6931188</v>
+        <v>6931251</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2949,7 +2939,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2976,10 +2966,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126931990</v>
+        <v>126932091</v>
       </c>
       <c r="B24" t="n">
-        <v>78773</v>
+        <v>57661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2987,34 +2977,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586783</v>
+        <v>586794</v>
       </c>
       <c r="R24" t="n">
-        <v>6931194</v>
+        <v>6931188</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3047,6 +3042,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3076,7 +3076,7 @@
         <v>126931781</v>
       </c>
       <c r="B25" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>126932116</v>
       </c>
       <c r="B26" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>126931803</v>
       </c>
       <c r="B27" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>126930037</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>126929983</v>
       </c>
       <c r="B29" t="n">
-        <v>98363</v>
+        <v>98367</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>126930443</v>
       </c>
       <c r="B30" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -889,38 +889,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126930782</v>
+        <v>126932059</v>
       </c>
       <c r="B4" t="n">
-        <v>57483</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102976</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -929,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586748</v>
+        <v>586799</v>
       </c>
       <c r="R4" t="n">
-        <v>6931372</v>
+        <v>6931194</v>
       </c>
       <c r="S4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,11 +964,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flyger över oss och gör läten</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,37 +990,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126932059</v>
+        <v>126930782</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>57483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102976</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1035,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586799</v>
+        <v>586748</v>
       </c>
       <c r="R5" t="n">
-        <v>6931194</v>
+        <v>6931372</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,6 +1066,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flyger över oss och gör läten</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1418,27 +1418,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126929962</v>
+        <v>126932136</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>57483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>102976</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1446,10 +1446,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1458,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586797</v>
+        <v>586790</v>
       </c>
       <c r="R9" t="n">
-        <v>6931496</v>
+        <v>6931174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,7 +1502,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Flyger ovanför oss.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,27 +1529,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126932136</v>
+        <v>126929962</v>
       </c>
       <c r="B10" t="n">
-        <v>57483</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1553,14 +1557,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586790</v>
+        <v>586797</v>
       </c>
       <c r="R10" t="n">
-        <v>6931174</v>
+        <v>6931496</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flyger ovanför oss.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2762,10 +2762,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126931990</v>
+        <v>126931480</v>
       </c>
       <c r="B22" t="n">
-        <v>78777</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2773,34 +2773,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586783</v>
+        <v>586733</v>
       </c>
       <c r="R22" t="n">
-        <v>6931194</v>
+        <v>6931251</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2833,6 +2838,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2859,7 +2869,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126931480</v>
+        <v>126932091</v>
       </c>
       <c r="B23" t="n">
         <v>57661</v>
@@ -2890,7 +2900,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2899,10 +2909,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586733</v>
+        <v>586794</v>
       </c>
       <c r="R23" t="n">
-        <v>6931251</v>
+        <v>6931188</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,7 +2949,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2966,10 +2976,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126932091</v>
+        <v>126931990</v>
       </c>
       <c r="B24" t="n">
-        <v>57661</v>
+        <v>78777</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2977,39 +2987,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586794</v>
+        <v>586783</v>
       </c>
       <c r="R24" t="n">
-        <v>6931188</v>
+        <v>6931194</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3042,11 +3047,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3387,45 +3387,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126930037</v>
+        <v>126929983</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>98367</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586781</v>
+        <v>586788</v>
       </c>
       <c r="R28" t="n">
-        <v>6931476</v>
+        <v>6931484</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,45 +3484,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126929983</v>
+        <v>126930037</v>
       </c>
       <c r="B29" t="n">
-        <v>98367</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586788</v>
+        <v>586781</v>
       </c>
       <c r="R29" t="n">
-        <v>6931484</v>
+        <v>6931476</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -889,37 +889,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126932059</v>
+        <v>126930782</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>57483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>102976</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -928,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586799</v>
+        <v>586748</v>
       </c>
       <c r="R4" t="n">
-        <v>6931194</v>
+        <v>6931372</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flyger över oss och gör läten</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,38 +996,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126930782</v>
+        <v>126932059</v>
       </c>
       <c r="B5" t="n">
-        <v>57483</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102976</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1030,13 +1035,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586748</v>
+        <v>586799</v>
       </c>
       <c r="R5" t="n">
-        <v>6931372</v>
+        <v>6931194</v>
       </c>
       <c r="S5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,11 +1071,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flyger över oss och gör läten</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1418,27 +1418,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126932136</v>
+        <v>126929962</v>
       </c>
       <c r="B9" t="n">
-        <v>57483</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1446,14 +1446,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1462,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586790</v>
+        <v>586797</v>
       </c>
       <c r="R9" t="n">
-        <v>6931174</v>
+        <v>6931496</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1498,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Flyger ovanför oss.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,27 +1525,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126929962</v>
+        <v>126932136</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>57483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>102976</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1557,10 +1553,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586797</v>
+        <v>586790</v>
       </c>
       <c r="R10" t="n">
-        <v>6931496</v>
+        <v>6931174</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Flyger ovanför oss.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2976,45 +2976,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126931990</v>
+        <v>126931781</v>
       </c>
       <c r="B24" t="n">
-        <v>78777</v>
+        <v>98447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586783</v>
+        <v>586763</v>
       </c>
       <c r="R24" t="n">
-        <v>6931194</v>
+        <v>6931228</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3047,6 +3051,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Blommar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3073,7 +3082,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126931781</v>
+        <v>126932116</v>
       </c>
       <c r="B25" t="n">
         <v>98447</v>
@@ -3103,7 +3112,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3112,10 +3121,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586763</v>
+        <v>586789</v>
       </c>
       <c r="R25" t="n">
-        <v>6931228</v>
+        <v>6931181</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,11 +3157,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Blommar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3179,49 +3183,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126932116</v>
+        <v>126931990</v>
       </c>
       <c r="B26" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586789</v>
+        <v>586783</v>
       </c>
       <c r="R26" t="n">
-        <v>6931181</v>
+        <v>6931194</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -889,38 +889,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126930782</v>
+        <v>126932059</v>
       </c>
       <c r="B4" t="n">
-        <v>57483</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102976</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -929,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586748</v>
+        <v>586799</v>
       </c>
       <c r="R4" t="n">
-        <v>6931372</v>
+        <v>6931194</v>
       </c>
       <c r="S4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,11 +964,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flyger över oss och gör läten</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,37 +990,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126932059</v>
+        <v>126930782</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>57483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102976</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1035,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586799</v>
+        <v>586748</v>
       </c>
       <c r="R5" t="n">
-        <v>6931194</v>
+        <v>6931372</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,6 +1066,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flyger över oss och gör läten</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1418,27 +1418,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126929962</v>
+        <v>126932136</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>57483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>102976</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1446,10 +1446,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1458,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586797</v>
+        <v>586790</v>
       </c>
       <c r="R9" t="n">
-        <v>6931496</v>
+        <v>6931174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,7 +1502,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Flyger ovanför oss.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,27 +1529,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126932136</v>
+        <v>126929962</v>
       </c>
       <c r="B10" t="n">
-        <v>57483</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1553,14 +1557,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586790</v>
+        <v>586797</v>
       </c>
       <c r="R10" t="n">
-        <v>6931174</v>
+        <v>6931496</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flyger ovanför oss.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2349,10 +2349,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126930790</v>
+        <v>126932045</v>
       </c>
       <c r="B18" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2360,42 +2360,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586748</v>
+        <v>586799</v>
       </c>
       <c r="R18" t="n">
-        <v>6931372</v>
+        <v>6931194</v>
       </c>
       <c r="S18" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2451,10 +2446,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126932045</v>
+        <v>126930790</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2462,37 +2457,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586799</v>
+        <v>586748</v>
       </c>
       <c r="R19" t="n">
-        <v>6931194</v>
+        <v>6931372</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2976,49 +2976,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126931781</v>
+        <v>126931990</v>
       </c>
       <c r="B24" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586763</v>
+        <v>586783</v>
       </c>
       <c r="R24" t="n">
-        <v>6931228</v>
+        <v>6931194</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3051,11 +3047,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Blommar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3082,7 +3073,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126932116</v>
+        <v>126931781</v>
       </c>
       <c r="B25" t="n">
         <v>98447</v>
@@ -3112,7 +3103,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>110</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3121,10 +3112,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586789</v>
+        <v>586763</v>
       </c>
       <c r="R25" t="n">
-        <v>6931181</v>
+        <v>6931228</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3157,6 +3148,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Blommar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,45 +3179,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126931990</v>
+        <v>126932116</v>
       </c>
       <c r="B26" t="n">
-        <v>78777</v>
+        <v>98447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586783</v>
+        <v>586789</v>
       </c>
       <c r="R26" t="n">
-        <v>6931194</v>
+        <v>6931181</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -889,37 +889,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126932059</v>
+        <v>126930782</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>57483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>102976</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -928,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586799</v>
+        <v>586748</v>
       </c>
       <c r="R4" t="n">
-        <v>6931194</v>
+        <v>6931372</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flyger över oss och gör läten</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,38 +996,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126930782</v>
+        <v>126932059</v>
       </c>
       <c r="B5" t="n">
-        <v>57483</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102976</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1030,13 +1035,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586748</v>
+        <v>586799</v>
       </c>
       <c r="R5" t="n">
-        <v>6931372</v>
+        <v>6931194</v>
       </c>
       <c r="S5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,11 +1071,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flyger över oss och gör läten</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1418,27 +1418,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126932136</v>
+        <v>126929962</v>
       </c>
       <c r="B9" t="n">
-        <v>57483</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1446,14 +1446,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1462,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586790</v>
+        <v>586797</v>
       </c>
       <c r="R9" t="n">
-        <v>6931174</v>
+        <v>6931496</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1498,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Flyger ovanför oss.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,27 +1525,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126929962</v>
+        <v>126932136</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>57483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>102976</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1557,10 +1553,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586797</v>
+        <v>586790</v>
       </c>
       <c r="R10" t="n">
-        <v>6931496</v>
+        <v>6931174</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Flyger ovanför oss.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2144,7 +2144,7 @@
         <v>126930960</v>
       </c>
       <c r="B16" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>126931781</v>
       </c>
       <c r="B25" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>126932116</v>
       </c>
       <c r="B26" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3387,45 +3387,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126929983</v>
+        <v>126930037</v>
       </c>
       <c r="B28" t="n">
-        <v>98367</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586788</v>
+        <v>586781</v>
       </c>
       <c r="R28" t="n">
-        <v>6931484</v>
+        <v>6931476</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,45 +3484,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126930037</v>
+        <v>126929983</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>98368</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586781</v>
+        <v>586788</v>
       </c>
       <c r="R29" t="n">
-        <v>6931476</v>
+        <v>6931484</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3584,7 +3584,7 @@
         <v>126930443</v>
       </c>
       <c r="B30" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -1636,7 +1636,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126930308</v>
+        <v>126930561</v>
       </c>
       <c r="B11" t="n">
         <v>79018</v>
@@ -1671,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586754</v>
+        <v>586743</v>
       </c>
       <c r="R11" t="n">
-        <v>6931449</v>
+        <v>6931411</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,7 +1733,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126930561</v>
+        <v>126930308</v>
       </c>
       <c r="B12" t="n">
         <v>79018</v>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586743</v>
+        <v>586754</v>
       </c>
       <c r="R12" t="n">
-        <v>6931411</v>
+        <v>6931449</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126930713</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126932017</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,38 +889,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126930782</v>
+        <v>126932059</v>
       </c>
       <c r="B4" t="n">
-        <v>57483</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102976</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -929,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586748</v>
+        <v>586799</v>
       </c>
       <c r="R4" t="n">
-        <v>6931372</v>
+        <v>6931194</v>
       </c>
       <c r="S4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,11 +964,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flyger över oss och gör läten</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,37 +990,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126932059</v>
+        <v>126930782</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>57485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102976</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1035,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586799</v>
+        <v>586748</v>
       </c>
       <c r="R5" t="n">
-        <v>6931194</v>
+        <v>6931372</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,6 +1066,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flyger över oss och gör läten</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,7 +1100,7 @@
         <v>126931093</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>126930683</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>126931252</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>126929962</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>126932136</v>
       </c>
       <c r="B10" t="n">
-        <v>57483</v>
+        <v>57485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>126930561</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>126930308</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>126929931</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126930379</v>
+        <v>126930081</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586799</v>
+        <v>586766</v>
       </c>
       <c r="R14" t="n">
-        <v>6931409</v>
+        <v>6931484</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126930081</v>
+        <v>126930379</v>
       </c>
       <c r="B15" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586766</v>
+        <v>586799</v>
       </c>
       <c r="R15" t="n">
-        <v>6931484</v>
+        <v>6931409</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2144,7 +2144,7 @@
         <v>126930960</v>
       </c>
       <c r="B16" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>126931404</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126932045</v>
+        <v>126930790</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>57823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2360,37 +2360,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586799</v>
+        <v>586748</v>
       </c>
       <c r="R18" t="n">
-        <v>6931194</v>
+        <v>6931372</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2446,10 +2451,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126930790</v>
+        <v>126932045</v>
       </c>
       <c r="B19" t="n">
-        <v>57821</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2457,42 +2462,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586748</v>
+        <v>586799</v>
       </c>
       <c r="R19" t="n">
-        <v>6931372</v>
+        <v>6931194</v>
       </c>
       <c r="S19" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>126930476</v>
       </c>
       <c r="B20" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>126931316</v>
       </c>
       <c r="B21" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>126931480</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>126932091</v>
       </c>
       <c r="B23" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>126931990</v>
       </c>
       <c r="B24" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>126931781</v>
       </c>
       <c r="B25" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>126932116</v>
       </c>
       <c r="B26" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>126931803</v>
       </c>
       <c r="B27" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>126930037</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>126929983</v>
       </c>
       <c r="B29" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>126930443</v>
       </c>
       <c r="B30" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -889,37 +889,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126932059</v>
+        <v>126930782</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>57485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>102976</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -928,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586799</v>
+        <v>586748</v>
       </c>
       <c r="R4" t="n">
-        <v>6931194</v>
+        <v>6931372</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flyger över oss och gör läten</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,38 +996,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126930782</v>
+        <v>126932059</v>
       </c>
       <c r="B5" t="n">
-        <v>57485</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102976</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1030,13 +1035,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586748</v>
+        <v>586799</v>
       </c>
       <c r="R5" t="n">
-        <v>6931372</v>
+        <v>6931194</v>
       </c>
       <c r="S5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,11 +1071,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flyger över oss och gör läten</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1927,7 +1927,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126930081</v>
+        <v>126930379</v>
       </c>
       <c r="B14" t="n">
         <v>57663</v>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586766</v>
+        <v>586799</v>
       </c>
       <c r="R14" t="n">
-        <v>6931484</v>
+        <v>6931409</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2034,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126930379</v>
+        <v>126930081</v>
       </c>
       <c r="B15" t="n">
         <v>57663</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586799</v>
+        <v>586766</v>
       </c>
       <c r="R15" t="n">
-        <v>6931409</v>
+        <v>6931484</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2349,10 +2349,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126930790</v>
+        <v>126932045</v>
       </c>
       <c r="B18" t="n">
-        <v>57823</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2360,42 +2360,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586748</v>
+        <v>586799</v>
       </c>
       <c r="R18" t="n">
-        <v>6931372</v>
+        <v>6931194</v>
       </c>
       <c r="S18" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2451,10 +2446,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126932045</v>
+        <v>126930790</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>57823</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2462,37 +2457,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586799</v>
+        <v>586748</v>
       </c>
       <c r="R19" t="n">
-        <v>6931194</v>
+        <v>6931372</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2976,45 +2976,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126931990</v>
+        <v>126932116</v>
       </c>
       <c r="B24" t="n">
-        <v>78779</v>
+        <v>98450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586783</v>
+        <v>586789</v>
       </c>
       <c r="R24" t="n">
-        <v>6931194</v>
+        <v>6931181</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3179,49 +3183,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126932116</v>
+        <v>126931990</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>78779</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586789</v>
+        <v>586783</v>
       </c>
       <c r="R26" t="n">
-        <v>6931181</v>
+        <v>6931194</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -1418,27 +1418,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126929962</v>
+        <v>126932136</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>102976</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1446,10 +1446,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1458,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586797</v>
+        <v>586790</v>
       </c>
       <c r="R9" t="n">
-        <v>6931496</v>
+        <v>6931174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,7 +1502,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Flyger ovanför oss.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,27 +1529,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126932136</v>
+        <v>126929962</v>
       </c>
       <c r="B10" t="n">
-        <v>57485</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1553,14 +1557,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586790</v>
+        <v>586797</v>
       </c>
       <c r="R10" t="n">
-        <v>6931174</v>
+        <v>6931496</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flyger ovanför oss.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2976,49 +2976,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126932116</v>
+        <v>126931990</v>
       </c>
       <c r="B24" t="n">
-        <v>98450</v>
+        <v>78779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586789</v>
+        <v>586783</v>
       </c>
       <c r="R24" t="n">
-        <v>6931181</v>
+        <v>6931194</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3077,7 +3073,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126931781</v>
+        <v>126932116</v>
       </c>
       <c r="B25" t="n">
         <v>98450</v>
@@ -3107,7 +3103,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3116,10 +3112,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586763</v>
+        <v>586789</v>
       </c>
       <c r="R25" t="n">
-        <v>6931228</v>
+        <v>6931181</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,11 +3148,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Blommar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,45 +3174,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126931990</v>
+        <v>126931781</v>
       </c>
       <c r="B26" t="n">
-        <v>78779</v>
+        <v>98450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586783</v>
+        <v>586763</v>
       </c>
       <c r="R26" t="n">
-        <v>6931194</v>
+        <v>6931228</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3254,6 +3249,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Blommar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3387,45 +3387,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126930037</v>
+        <v>126929983</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>98370</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586781</v>
+        <v>586788</v>
       </c>
       <c r="R28" t="n">
-        <v>6931476</v>
+        <v>6931484</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,45 +3484,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126929983</v>
+        <v>126930037</v>
       </c>
       <c r="B29" t="n">
-        <v>98370</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586788</v>
+        <v>586781</v>
       </c>
       <c r="R29" t="n">
-        <v>6931484</v>
+        <v>6931476</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126930713</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126932017</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>126931093</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>126930683</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>126931252</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>126929962</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>126930379</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>126930081</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>126931404</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>126930476</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>126931316</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>126931480</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>126932091</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126930713</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126932017</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>126931093</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>126930683</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>126931252</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>126929962</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>126930379</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>126930081</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>126931404</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>126930476</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>126931316</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>126931480</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>126932091</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 53736-2023 artfynd.xlsx
+++ b/artfynd/A 53736-2023 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>126930782</v>
       </c>
       <c r="B4" t="n">
-        <v>57485</v>
+        <v>57479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126932059</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>126932136</v>
       </c>
       <c r="B9" t="n">
-        <v>57485</v>
+        <v>57479</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126930561</v>
+        <v>126930308</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586743</v>
+        <v>586754</v>
       </c>
       <c r="R11" t="n">
-        <v>6931411</v>
+        <v>6931449</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,10 +1733,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126930308</v>
+        <v>126930561</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586754</v>
+        <v>586743</v>
       </c>
       <c r="R12" t="n">
-        <v>6931449</v>
+        <v>6931411</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,7 +1833,7 @@
         <v>126929931</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>126930960</v>
       </c>
       <c r="B16" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>126932045</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>126930790</v>
       </c>
       <c r="B19" t="n">
-        <v>57823</v>
+        <v>57817</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,38 +2762,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126931480</v>
+        <v>126931781</v>
       </c>
       <c r="B22" t="n">
-        <v>57741</v>
+        <v>98436</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>110</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2802,10 +2801,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586733</v>
+        <v>586763</v>
       </c>
       <c r="R22" t="n">
-        <v>6931251</v>
+        <v>6931228</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,7 +2841,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Blommar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2869,38 +2868,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126932091</v>
+        <v>126932116</v>
       </c>
       <c r="B23" t="n">
-        <v>57741</v>
+        <v>98436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2909,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586794</v>
+        <v>586789</v>
       </c>
       <c r="R23" t="n">
-        <v>6931188</v>
+        <v>6931181</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2945,11 +2943,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2976,10 +2969,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126931990</v>
+        <v>126931480</v>
       </c>
       <c r="B24" t="n">
-        <v>78779</v>
+        <v>57741</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2987,34 +2980,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586783</v>
+        <v>586733</v>
       </c>
       <c r="R24" t="n">
-        <v>6931194</v>
+        <v>6931251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3047,6 +3045,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3073,37 +3076,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126932116</v>
+        <v>126932091</v>
       </c>
       <c r="B25" t="n">
-        <v>98450</v>
+        <v>57741</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3112,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586789</v>
+        <v>586794</v>
       </c>
       <c r="R25" t="n">
-        <v>6931181</v>
+        <v>6931188</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,6 +3152,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3174,49 +3183,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126931781</v>
+        <v>126931990</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>78770</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586763</v>
+        <v>586783</v>
       </c>
       <c r="R26" t="n">
-        <v>6931228</v>
+        <v>6931194</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3249,11 +3254,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Blommar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3283,7 +3283,7 @@
         <v>126931803</v>
       </c>
       <c r="B27" t="n">
-        <v>92622</v>
+        <v>92609</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,45 +3387,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126929983</v>
+        <v>126930037</v>
       </c>
       <c r="B28" t="n">
-        <v>98370</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586788</v>
+        <v>586781</v>
       </c>
       <c r="R28" t="n">
-        <v>6931484</v>
+        <v>6931476</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,45 +3484,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126930037</v>
+        <v>126929983</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>98356</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586781</v>
+        <v>586788</v>
       </c>
       <c r="R29" t="n">
-        <v>6931476</v>
+        <v>6931484</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3584,7 +3584,7 @@
         <v>126930443</v>
       </c>
       <c r="B30" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
